--- a/reports/Debug-purgatory-20260104/For The Week Ending (Prior Year)_Payroll_history.xlsx
+++ b/reports/Debug-purgatory-20260104/For The Week Ending (Prior Year)_Payroll_history.xlsx
@@ -31,6 +31,24 @@
     <t>D8050</t>
   </si>
   <si>
+    <t>D2200</t>
+  </si>
+  <si>
+    <t>D3000</t>
+  </si>
+  <si>
+    <t>D4055</t>
+  </si>
+  <si>
+    <t>D5209</t>
+  </si>
+  <si>
+    <t>D6780</t>
+  </si>
+  <si>
+    <t>D8020</t>
+  </si>
+  <si>
     <t>D2000</t>
   </si>
   <si>
@@ -55,22 +73,25 @@
     <t>D5810</t>
   </si>
   <si>
-    <t>D2200</t>
-  </si>
-  <si>
-    <t>D3000</t>
-  </si>
-  <si>
-    <t>D4055</t>
-  </si>
-  <si>
-    <t>D5209</t>
-  </si>
-  <si>
-    <t>D6780</t>
-  </si>
-  <si>
-    <t>D8020</t>
+    <t>D1020</t>
+  </si>
+  <si>
+    <t>D1070</t>
+  </si>
+  <si>
+    <t>D5000</t>
+  </si>
+  <si>
+    <t>D5201</t>
+  </si>
+  <si>
+    <t>D5208</t>
+  </si>
+  <si>
+    <t>D6781</t>
+  </si>
+  <si>
+    <t>D8040</t>
   </si>
   <si>
     <t>D1000</t>
@@ -89,27 +110,6 @@
   </si>
   <si>
     <t>D6790</t>
-  </si>
-  <si>
-    <t>D1020</t>
-  </si>
-  <si>
-    <t>D1070</t>
-  </si>
-  <si>
-    <t>D5000</t>
-  </si>
-  <si>
-    <t>D5201</t>
-  </si>
-  <si>
-    <t>D5208</t>
-  </si>
-  <si>
-    <t>D6781</t>
-  </si>
-  <si>
-    <t>D8040</t>
   </si>
   <si>
     <t>D1010</t>
@@ -563,7 +563,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="2">
-        <v>68423.32</v>
+        <v>2191.44</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -571,7 +571,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="2">
-        <v>20320.64</v>
+        <v>12828.23</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -579,7 +579,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="2">
-        <v>1419.36</v>
+        <v>4433.54</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -587,7 +587,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="2">
-        <v>2440.43</v>
+        <v>2805.62</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -595,7 +595,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="2">
-        <v>7855.19</v>
+        <v>18378.84</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -603,7 +603,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>6076.06</v>
+        <v>4166.20</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -611,7 +611,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="2">
-        <v>276.58</v>
+        <v>68423.32</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -619,7 +619,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>1371.16</v>
+        <v>20320.64</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -627,7 +627,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>2191.44</v>
+        <v>1419.36</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -635,7 +635,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>12828.23</v>
+        <v>2440.43</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -643,7 +643,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2">
-        <v>4433.54</v>
+        <v>7855.19</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -651,7 +651,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>2805.62</v>
+        <v>6076.06</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -659,7 +659,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>18378.84</v>
+        <v>276.58</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -667,7 +667,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2">
-        <v>4166.20</v>
+        <v>1371.16</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -675,7 +675,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>2030.28</v>
+        <v>14580.01</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -683,7 +683,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>9057.77</v>
+        <v>15131.13</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -691,7 +691,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>4154.68</v>
+        <v>12451.65</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -699,7 +699,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>9721.72</v>
+        <v>7737.85</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -707,7 +707,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2">
-        <v>3285.93</v>
+        <v>23127.37</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -715,7 +715,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2">
-        <v>14710.02</v>
+        <v>436.25</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -723,7 +723,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2">
-        <v>14580.01</v>
+        <v>4700.38</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -731,7 +731,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>15131.13</v>
+        <v>2030.28</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -739,7 +739,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="2">
-        <v>12451.65</v>
+        <v>9057.77</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -747,7 +747,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="2">
-        <v>7737.85</v>
+        <v>4154.68</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -755,7 +755,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>23127.37</v>
+        <v>9721.72</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -763,7 +763,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>436.25</v>
+        <v>3285.93</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -771,7 +771,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>4700.38</v>
+        <v>14710.02</v>
       </c>
     </row>
     <row r="33" spans="1:2">
